--- a/dados/excel/quadro_escolaridade.xlsx
+++ b/dados/excel/quadro_escolaridade.xlsx
@@ -7,18 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metadados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +32,37 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000D2B4E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004A5568"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +71,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00003A70"/>
-        <bgColor rgb="00003A70"/>
+        <fgColor rgb="000D2B4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,25 +89,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color rgb="004A90D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D8DEE6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D8DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D8DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D8DEE6"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,370 +509,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ESCOLARIDADE</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>REGISTROS</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>MATRÍCULAS ÚNICAS</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA BRUTA (R$)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA MÉDIA (R$)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FOLHA MEDIANA (R$)</t>
+          <t>Escolaridade (contagem)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>4228667.73</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>3768.866069518717</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>3557.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Fundamental incompleto</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>6492</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>31288152.6</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>4819.493622920518</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>4483.9</t>
+          <t>Fonte: Portal da Transparência de Sorocaba · Organizado pelo Observatório Social do Brasil — Sorocaba · Licença CC-BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Fundamental completo</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20581</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89061024.26</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4327.341929935377</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3803.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Médio incompleto</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11653800.0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5546.787244169444</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4688.18</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Para que serve</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Formação geral.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Médio completo</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>204854</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5396</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>948405514.73</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4629.665589785896</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4030.895</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Informações técnicas</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Superior incompleto</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>64842</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4890</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>123089483.96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1898.298694673205</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1084.8</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>quadro_escolaridade.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Superior completo</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>397517</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12793</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2882452292.07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7251.142195352652</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5780.56</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Servidores por nível.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Pós-graduação</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>142215</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1609869511.64</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11319.96984593749</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10389.33</t>
-        </is>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Linhas</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Mestrado</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>8492</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>121749434.31</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14336.956466085729</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12349.495</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Colunas</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Doutorado</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34858622.41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15149.33611907866</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13583.51</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Separador</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ponto e vírgula</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Codificação</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gerado em</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>24/09/2026 19:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dicionário de colunas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Coluna</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Formato no Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>﻿escolaridade_canonica</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>num_registros</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>num_matriculas</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Número decimal (#,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>folha_total</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>folha_media</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>folha_mediana</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -817,86 +772,271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CAMPO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>﻿escolaridade_canonica</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>num_registros</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>num_matriculas</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>folha_total</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>folha_media</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>folha_mediana</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>FONTE</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Portal da Transparência de Sorocaba</t>
-        </is>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Sem escolaridade formal registrada</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>1122</v>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>4228667.73</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>3768.866069518717</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>3557.91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>https://transparencia.sorocaba.sp.gov.br</t>
-        </is>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Fundamental incompleto</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>6492</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>31288152.6</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>4819.493622920518</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>4483.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PERÍODO</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2022-01 a 2026-08</t>
-        </is>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Fundamental completo</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>20581</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>459</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>89061024.26000001</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>4327.341929935377</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>3803.64</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LICENÇA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>CC-BY 4.0 — Observatório Social do Brasil — Sorocaba</t>
-        </is>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Medio incompleto</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2101</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>11653800</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>5546.787244169444</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>4688.18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>GERADO EM</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23 18:50</t>
-        </is>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Medio completo</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>204854</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>5396</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>948405514.73</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>4629.665589785896</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>4030.895</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>64842</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>4890</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>123089483.96</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1898.298694673206</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1084.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>397517</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>12793</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>2882452292.07</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>7251.142195352652</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>5780.56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Pos-graduacao</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>142215</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>2852</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1609869511.64</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>11319.96984593749</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>10389.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>8492</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>121749434.31</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>14336.95646608573</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>12349.495</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>34858622.41</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>15149.33611907866</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>13583.51</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/excel/quadro_escolaridade.xlsx
+++ b/dados/excel/quadro_escolaridade.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="C2" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>4228667.73</v>
+        <v>4275760.42</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>3768.866069518717</v>
+        <v>3773.83973521624</v>
       </c>
       <c r="F2" s="10" t="n">
         <v>3557.91</v>
@@ -844,19 +844,19 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>6492</v>
+        <v>6563</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>127</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>31288152.6</v>
+        <v>31792568.1</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>4819.493622920518</v>
+        <v>4844.212722840165</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>4483.9</v>
+        <v>4508.1</v>
       </c>
     </row>
     <row r="4">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>20581</v>
+        <v>20879</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>89061024.26000001</v>
+        <v>90648395.76000001</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>4327.341929935377</v>
+        <v>4341.606195699028</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>3803.64</v>
+        <v>3814.93</v>
       </c>
     </row>
     <row r="5">
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>54</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>11653800</v>
+        <v>11807245.19</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>5546.787244169444</v>
+        <v>5566.829415370108</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>4688.18</v>
+        <v>4716.58</v>
       </c>
     </row>
     <row r="6">
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>204854</v>
+        <v>208747</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>5396</v>
+        <v>5453</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>948405514.73</v>
+        <v>971162134.8200001</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>4629.665589785896</v>
+        <v>4652.340559720619</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4030.895</v>
+        <v>4053.7</v>
       </c>
     </row>
     <row r="7">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>64842</v>
+        <v>65847</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>4890</v>
+        <v>4949</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>123089483.96</v>
+        <v>125494791.34</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1898.298694673206</v>
+        <v>1905.85434932495</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>1084.8</v>
@@ -954,19 +954,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>397517</v>
+        <v>405257</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>12793</v>
+        <v>13064</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>2882452292.07</v>
+        <v>2949472775.14</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>7251.142195352652</v>
+        <v>7278.030423015518</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5780.56</v>
+        <v>5804</v>
       </c>
     </row>
     <row r="9">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>142215</v>
+        <v>144273</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>2852</v>
+        <v>2856</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1609869511.64</v>
+        <v>1642060187.22</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>11319.96984593749</v>
+        <v>11381.61809361419</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>10389.33</v>
+        <v>10434.34</v>
       </c>
     </row>
     <row r="10">
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>8492</v>
+        <v>8620</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>145</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>121749434.31</v>
+        <v>124353069.99</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>14336.95646608573</v>
+        <v>14426.11020765661</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>12349.495</v>
+        <v>12423.755</v>
       </c>
     </row>
     <row r="11">
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2301</v>
+        <v>2332</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>34858622.41</v>
+        <v>35560795.55</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>15149.33611907866</v>
+        <v>15249.05469554031</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>13583.51</v>
+        <v>13739.985</v>
       </c>
     </row>
   </sheetData>
